--- a/Immobiliare.xlsx
+++ b/Immobiliare.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dati Immobiliare" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Dati OMI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,346 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Prezzo</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>MQ</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Prezzo/MQ</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Vani</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Piano</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Piano descr.</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Anno 2021 - Semestre 2 </t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Provincia</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>PESCARA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Fascia</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Centrale/- AREE A NORD DEL PORTO CANALE FINO A VIA BALILLA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Comune</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PESCARA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Zona</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Tipologia</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Pr. min</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Pr. max</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Pr.Aff. min</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Pr.Aff. max</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Abitazioni civili</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Ottimo</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3200</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>5,8</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>8,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Abitazioni civili</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Normale</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Abitazioni di tipo economico</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Normale</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>3,5</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>5,2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Box</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Normale</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1700</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>5,4</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>7,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Posti auto coperti</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Normale</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1150</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>3,4</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>5,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Posti auto scoperti</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Normale</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>2,3</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Ville e Villini</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Normale</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1550</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>5,3</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>7,2</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Immobiliare.xlsx
+++ b/Immobiliare.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dati Immobiliare" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dati OMI" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,9 +414,1816 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Prezzo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>MQ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Prezzo/MQ</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Vani</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Piano</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Piano descr.</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>115000</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1017.7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4 locali</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>nuovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>127000</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2645.83</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2 locali</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>139000</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2278.69</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2 locali</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>143000</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>145000</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1611.11</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>terra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>152000</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2268.66</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>155000</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2384.62</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>155000</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2384.62</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>160000</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>4 locali</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>terzo</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>163000</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2507.69</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>167000</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2385.71</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>179000</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>203.41</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5 locali</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>219000</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>817.16</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>220000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1913.04</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4 locali</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>terzo</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>230000</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2875</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>terzo</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>230000</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2875</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>terzo</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nuovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>239000</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1838.46</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4 locali</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>360000</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1658.99</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5 locali</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>445000</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>910.02</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>5+ locali</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>55000</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1375</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2 locali</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>68000</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1942.86</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2 locali</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>95000</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1900</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2 locali</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>terzo</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>99000</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1269.23</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>secondo</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>recente</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>990000</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1394</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>710.1900000000001</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5+ locali</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>prezzo su richiesta</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5+ locali</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ottimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>103000</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1391.89</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>109000</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1816.67</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>secondo</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>119000</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1983.33</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>120000</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>4 locali</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>secondo</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>ristrutturato</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>129000</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2150</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2 locali</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>154000</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3019.61</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2 - 3 locali</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>nuovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>155000</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2123.29</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>terra</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>157000</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1236.22</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>158000</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2358.21</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>terra</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>nuovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>165000</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2357.14</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>secondo</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>170000</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2833.33</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>terzo</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>179000</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1409.45</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>4 locali</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>220000</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>4150.94</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2 locali</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2500000</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1282.05</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>5+ locali</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>ottimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>255125</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>4252.08</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>5+ locali</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>275000</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2067.67</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4 locali</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>278000</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4343.75</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>3 - 4 locali</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>terra</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>nuovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>358000</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1790</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5 locali</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>recente</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>388500</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>4980.77</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>nuovo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>390000</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2378.05</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>5+ locali</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>449000</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>4081.82</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4 locali</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>secondo</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>85000</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2833.33</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1 locale</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>terzo</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>92912</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>619.41</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>5+ locali</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>primo</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>99000</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1076.09</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3 locali</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>terzo</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>prezzo su richiesta</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>4 locali</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>nuovo</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anno 2021 - Semestre 2 </t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Provincia</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>PESCARA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Fascia</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Centrale/- AREE A NORD DEL PORTO CANALE FINO A VIA BALILLA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Comune</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PESCARA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tipologia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pr. min</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Pr. max</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pr.Aff. min</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pr.Aff. max</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Abitazioni civili</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ottimo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2050</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>5,8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Abitazioni civili</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Normale</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Abitazioni di tipo economico</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Normale</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3,5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5,2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Box</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Normale</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>5,4</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>7,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Posti auto coperti</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Normale</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1150</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5,1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Posti auto scoperti</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Normale</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2,3</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>3,4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ville e Villini</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Normale</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>5,3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>7,2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>